--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  09.06.2025 a 15.06.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  09.06.2025 a 15.06.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29010"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D0D816E-D6E3-4234-898C-C454D71AC074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE9E33E9-938A-44DB-B1B1-FB14CE054F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="09.06" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="94">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -254,6 +254,91 @@
   </si>
   <si>
     <t xml:space="preserve">WAGNER LUIZ ANDRADE CPF 08175085622          </t>
+  </si>
+  <si>
+    <t>EDILAINE PINHO RIBEIRO DOS SANTOS CPF  9980263792</t>
+  </si>
+  <si>
+    <t>Chassi irregular</t>
+  </si>
+  <si>
+    <t>ADAIR LUCIO DE AQUINO CPF  3701496617</t>
+  </si>
+  <si>
+    <t>Não existe código FIPE para este chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILENA DE SOUSA CASTRO                       </t>
+  </si>
+  <si>
+    <t>a pedido segurado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAURI RODRIGUES                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOVIS FINGER                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JONY TEIXEIRA SILVA                          </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA: Chassi (Impossibilidade de leitura completa do chassi).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELSO INOCENCIO DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KATIELE APARECIDA DA SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KENNY PIRES MENDES                           </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para o(a) senhor(a
+) KENNY PIRES MENDES, pois este não consta como condutor na apólic
+eanterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARINE INOUE INADA                           </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senho
+r(a) MARINE INOUE INADA, pois este não consta como condutor na apó
+lice anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOLTEC NE SERVICOS METALURGICOS REPARACAO DE </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para o(a) senhor(a
+) MOLTEC NE SERVICOS METALURGICOS REPARAC, pois segurado anterior
+JOSE CARLOS DE SOUZA OLIVEIRA não consta no quadro societário da e
+mpresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE HENRIQUE DA SILVA                       </t>
+  </si>
+  <si>
+    <t>Nup CANCELAMENTO 11/06/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE BASTOS DA SILVA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THYAGO MARCELO SOARES ARAUJO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANA ROSA DE JESUS LISBOA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEMIR LOPES                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXSANDRA MEDEIROS GOMES                    </t>
   </si>
 </sst>
 </file>
@@ -485,7 +570,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -593,29 +678,23 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -2666,7 +2745,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2716,22 +2795,22 @@
       <c r="B2" s="7">
         <v>45806</v>
       </c>
-      <c r="C2" s="44">
+      <c r="C2" s="43">
         <v>45819</v>
       </c>
-      <c r="D2" s="43">
+      <c r="D2" s="21">
         <v>132747887</v>
       </c>
       <c r="E2" s="18">
         <v>3449994691</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="21" t="s">
         <v>50</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I2" s="23">
@@ -2745,16 +2824,16 @@
       <c r="B3" s="7">
         <v>45811</v>
       </c>
-      <c r="C3" s="44">
+      <c r="C3" s="43">
         <v>45819</v>
       </c>
-      <c r="D3" s="43">
+      <c r="D3" s="21">
         <v>132817767</v>
       </c>
       <c r="E3" s="18">
         <v>3449997881</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="21" t="s">
         <v>52</v>
       </c>
       <c r="G3" s="19" t="s">
@@ -2774,16 +2853,16 @@
       <c r="B4" s="7">
         <v>45812</v>
       </c>
-      <c r="C4" s="44">
+      <c r="C4" s="43">
         <v>45819</v>
       </c>
-      <c r="D4" s="43">
+      <c r="D4" s="21">
         <v>132829246</v>
       </c>
       <c r="E4" s="18">
         <v>3449998431</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="21" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="19" t="s">
@@ -2803,16 +2882,16 @@
       <c r="B5" s="7">
         <v>45812</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="43">
         <v>45819</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="21">
         <v>132833591</v>
       </c>
       <c r="E5" s="18">
         <v>3449998739</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="21" t="s">
         <v>55</v>
       </c>
       <c r="G5" s="19" t="s">
@@ -2832,16 +2911,16 @@
       <c r="B6" s="7">
         <v>45812</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="43">
         <v>45819</v>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="21">
         <v>132841043</v>
       </c>
       <c r="E6" s="18">
         <v>3449999190</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="21" t="s">
         <v>57</v>
       </c>
       <c r="G6" s="19" t="s">
@@ -2861,16 +2940,16 @@
       <c r="B7" s="7">
         <v>45813</v>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="43">
         <v>45819</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="21">
         <v>132856451</v>
       </c>
       <c r="E7" s="18">
         <v>3450000059</v>
       </c>
-      <c r="F7" s="43" t="s">
+      <c r="F7" s="21" t="s">
         <v>59</v>
       </c>
       <c r="G7" s="19" t="s">
@@ -2890,16 +2969,16 @@
       <c r="B8" s="7">
         <v>45814</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="43">
         <v>45819</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="21">
         <v>132876276</v>
       </c>
       <c r="E8" s="18">
         <v>3450001137</v>
       </c>
-      <c r="F8" s="43" t="s">
+      <c r="F8" s="21" t="s">
         <v>61</v>
       </c>
       <c r="G8" s="19" t="s">
@@ -2919,16 +2998,16 @@
       <c r="B9" s="7">
         <v>45812</v>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="43">
         <v>45819</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="21">
         <v>132826138</v>
       </c>
       <c r="E9" s="18">
         <v>3449998222</v>
       </c>
-      <c r="F9" s="43" t="s">
+      <c r="F9" s="21" t="s">
         <v>62</v>
       </c>
       <c r="G9" s="19" t="s">
@@ -2948,16 +3027,16 @@
       <c r="B10" s="7">
         <v>45812</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="43">
         <v>45819</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="21">
         <v>132832120</v>
       </c>
       <c r="E10" s="18">
         <v>3449998662</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="21" t="s">
         <v>63</v>
       </c>
       <c r="G10" s="19" t="s">
@@ -2977,16 +3056,16 @@
       <c r="B11" s="7">
         <v>45811</v>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="43">
         <v>45819</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="21">
         <v>132825408</v>
       </c>
       <c r="E11" s="18">
         <v>3449998057</v>
       </c>
-      <c r="F11" s="43" t="s">
+      <c r="F11" s="21" t="s">
         <v>64</v>
       </c>
       <c r="G11" s="19" t="s">
@@ -3006,16 +3085,16 @@
       <c r="B12" s="7">
         <v>45811</v>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="43">
         <v>45819</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="21">
         <v>132817972</v>
       </c>
       <c r="E12" s="18">
         <v>3449997914</v>
       </c>
-      <c r="F12" s="43" t="s">
+      <c r="F12" s="21" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="19" t="s">
@@ -3035,22 +3114,22 @@
       <c r="B13" s="7">
         <v>45811</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="43">
         <v>45819</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="21">
         <v>132817789</v>
       </c>
       <c r="E13" s="18">
         <v>3449997892</v>
       </c>
-      <c r="F13" s="43" t="s">
+      <c r="F13" s="21" t="s">
         <v>66</v>
       </c>
       <c r="G13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="53" t="s">
+      <c r="H13" s="9" t="s">
         <v>67</v>
       </c>
       <c r="I13" s="23">
@@ -3064,16 +3143,16 @@
       <c r="B14" s="25">
         <v>45813</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="43">
         <v>45819</v>
       </c>
-      <c r="D14" s="52">
+      <c r="D14" s="29">
         <v>132849470</v>
       </c>
       <c r="E14" s="30">
         <v>3449999586</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="F14" s="29" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="32" t="s">
@@ -3097,370 +3176,352 @@
       <c r="H15" s="13"/>
       <c r="I15" s="23"/>
     </row>
-    <row r="16" spans="1:9" s="49" customFormat="1">
-      <c r="A16" s="45"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="45"/>
-      <c r="I16" s="50"/>
-    </row>
-    <row r="17" spans="1:9" s="49" customFormat="1">
-      <c r="A17" s="45"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="45"/>
-      <c r="I17" s="50"/>
-    </row>
-    <row r="18" spans="1:9" s="49" customFormat="1">
-      <c r="A18" s="45"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="45"/>
-      <c r="I18" s="50"/>
-    </row>
-    <row r="19" spans="1:9" s="49" customFormat="1">
-      <c r="A19" s="45"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="G19" s="45"/>
-    </row>
-    <row r="20" spans="1:9" s="49" customFormat="1">
-      <c r="A20" s="45"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="G20" s="45"/>
-    </row>
-    <row r="21" spans="1:9" s="49" customFormat="1">
-      <c r="A21" s="45"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="G21" s="45"/>
-    </row>
-    <row r="22" spans="1:9" s="49" customFormat="1">
-      <c r="A22" s="45"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="G22" s="45"/>
-    </row>
-    <row r="23" spans="1:9" s="49" customFormat="1">
-      <c r="A23" s="45"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="G23" s="45"/>
-    </row>
-    <row r="24" spans="1:9" s="49" customFormat="1">
-      <c r="A24" s="45"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="G24" s="45"/>
-    </row>
-    <row r="25" spans="1:9" s="49" customFormat="1">
-      <c r="A25" s="45"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="G25" s="45"/>
-    </row>
-    <row r="26" spans="1:9" s="49" customFormat="1">
-      <c r="A26" s="45"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="G26" s="45"/>
-    </row>
-    <row r="27" spans="1:9" s="49" customFormat="1">
-      <c r="A27" s="45"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="G27" s="45"/>
-    </row>
-    <row r="28" spans="1:9" s="49" customFormat="1">
-      <c r="A28" s="45"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="G28" s="45"/>
-    </row>
-    <row r="29" spans="1:9" s="49" customFormat="1">
-      <c r="A29" s="45"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="G29" s="45"/>
-    </row>
-    <row r="30" spans="1:9" s="49" customFormat="1">
-      <c r="A30" s="45"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="G30" s="45"/>
-    </row>
-    <row r="31" spans="1:9" s="49" customFormat="1">
-      <c r="A31" s="45"/>
-      <c r="B31" s="47"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="G31" s="45"/>
-    </row>
-    <row r="32" spans="1:9" s="49" customFormat="1">
-      <c r="A32" s="45"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="G32" s="45"/>
-    </row>
-    <row r="33" spans="1:7" s="49" customFormat="1">
-      <c r="A33" s="45"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="G33" s="45"/>
-    </row>
-    <row r="34" spans="1:7" s="49" customFormat="1">
-      <c r="A34" s="45"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="G34" s="45"/>
-    </row>
-    <row r="35" spans="1:7" s="49" customFormat="1">
-      <c r="A35" s="45"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="G35" s="45"/>
-    </row>
-    <row r="36" spans="1:7" s="49" customFormat="1">
-      <c r="A36" s="45"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="G36" s="45"/>
-    </row>
-    <row r="37" spans="1:7" s="49" customFormat="1">
-      <c r="A37" s="45"/>
-      <c r="B37" s="47"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="G37" s="45"/>
-    </row>
-    <row r="38" spans="1:7" s="49" customFormat="1">
-      <c r="A38" s="45"/>
-      <c r="B38" s="47"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="G38" s="45"/>
-    </row>
-    <row r="39" spans="1:7" s="49" customFormat="1">
-      <c r="A39" s="45"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="G39" s="45"/>
-    </row>
-    <row r="40" spans="1:7" s="49" customFormat="1">
-      <c r="A40" s="45"/>
-      <c r="B40" s="47"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="G40" s="45"/>
-    </row>
-    <row r="41" spans="1:7" s="49" customFormat="1">
-      <c r="A41" s="45"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="G41" s="45"/>
-    </row>
-    <row r="42" spans="1:7" s="49" customFormat="1">
-      <c r="A42" s="45"/>
-      <c r="B42" s="47"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="G42" s="45"/>
-    </row>
-    <row r="43" spans="1:7" s="49" customFormat="1">
-      <c r="A43" s="45"/>
-      <c r="B43" s="47"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="G43" s="45"/>
-    </row>
-    <row r="44" spans="1:7" s="49" customFormat="1">
-      <c r="A44" s="45"/>
-      <c r="B44" s="47"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="G44" s="45"/>
-    </row>
-    <row r="45" spans="1:7" s="49" customFormat="1">
-      <c r="A45" s="45"/>
-      <c r="B45" s="47"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="G45" s="45"/>
-    </row>
-    <row r="46" spans="1:7" s="49" customFormat="1">
-      <c r="A46" s="45"/>
-      <c r="B46" s="47"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="G46" s="45"/>
-    </row>
-    <row r="47" spans="1:7" s="49" customFormat="1">
-      <c r="A47" s="45"/>
-      <c r="B47" s="47"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="G47" s="45"/>
-    </row>
-    <row r="48" spans="1:7" s="49" customFormat="1">
-      <c r="A48" s="45"/>
-      <c r="B48" s="47"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="G48" s="45"/>
-    </row>
-    <row r="49" spans="1:9" s="49" customFormat="1">
-      <c r="A49" s="45"/>
-      <c r="B49" s="47"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="G49" s="45"/>
-    </row>
-    <row r="50" spans="1:9" s="49" customFormat="1">
-      <c r="A50" s="45"/>
-      <c r="B50" s="47"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="G50" s="45"/>
-    </row>
-    <row r="51" spans="1:9" s="49" customFormat="1">
-      <c r="A51" s="45"/>
-      <c r="B51" s="47"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="G51" s="45"/>
-    </row>
-    <row r="52" spans="1:9" s="49" customFormat="1">
-      <c r="A52" s="45"/>
-      <c r="B52" s="47"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="G52" s="45"/>
-    </row>
-    <row r="53" spans="1:9" s="49" customFormat="1">
-      <c r="A53" s="45"/>
-      <c r="B53" s="47"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="47"/>
-      <c r="G53" s="45"/>
-    </row>
-    <row r="54" spans="1:9" s="49" customFormat="1">
-      <c r="A54" s="45"/>
-      <c r="B54" s="47"/>
-      <c r="C54" s="46"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="47"/>
-      <c r="G54" s="45"/>
-    </row>
-    <row r="55" spans="1:9" s="49" customFormat="1">
-      <c r="A55" s="45"/>
-      <c r="B55" s="47"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="G55" s="45"/>
-    </row>
-    <row r="56" spans="1:9" s="49" customFormat="1">
-      <c r="I56" s="51"/>
-    </row>
-    <row r="57" spans="1:9" s="49" customFormat="1">
-      <c r="I57" s="51"/>
-    </row>
-    <row r="58" spans="1:9" s="49" customFormat="1">
-      <c r="I58" s="51"/>
-    </row>
-    <row r="59" spans="1:9" s="49" customFormat="1">
-      <c r="I59" s="51"/>
-    </row>
-    <row r="60" spans="1:9" s="49" customFormat="1">
-      <c r="I60" s="51"/>
-    </row>
-    <row r="61" spans="1:9" s="49" customFormat="1">
-      <c r="I61" s="51"/>
-    </row>
-    <row r="62" spans="1:9" s="49" customFormat="1">
-      <c r="I62" s="51"/>
-    </row>
-    <row r="63" spans="1:9" s="49" customFormat="1">
-      <c r="I63" s="51"/>
-    </row>
-    <row r="64" spans="1:9" s="49" customFormat="1">
-      <c r="I64" s="51"/>
-    </row>
-    <row r="65" spans="9:9" s="49" customFormat="1">
-      <c r="I65" s="51"/>
-    </row>
-    <row r="66" spans="9:9" s="49" customFormat="1">
-      <c r="I66" s="51"/>
-    </row>
-    <row r="67" spans="9:9" s="49" customFormat="1">
-      <c r="I67" s="51"/>
-    </row>
-    <row r="68" spans="9:9" s="49" customFormat="1">
-      <c r="I68" s="51"/>
+    <row r="16" spans="1:9">
+      <c r="A16" s="22"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="22"/>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="22"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="22"/>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="22"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="22"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="22"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="G19" s="22"/>
+      <c r="I19"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="22"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="G20" s="22"/>
+      <c r="I20"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="22"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="G21" s="22"/>
+      <c r="I21"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="22"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="G22" s="22"/>
+      <c r="I22"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="22"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="G23" s="22"/>
+      <c r="I23"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="22"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="G24" s="22"/>
+      <c r="I24"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="22"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="G25" s="22"/>
+      <c r="I25"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="22"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="G26" s="22"/>
+      <c r="I26"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="22"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="G27" s="22"/>
+      <c r="I27"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="22"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="G28" s="22"/>
+      <c r="I28"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="22"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="G29" s="22"/>
+      <c r="I29"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="22"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="G30" s="22"/>
+      <c r="I30"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="22"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="G31" s="22"/>
+      <c r="I31"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="22"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="G32" s="22"/>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:7" customFormat="1">
+      <c r="A33" s="22"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" spans="1:7" customFormat="1">
+      <c r="A34" s="22"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" spans="1:7" customFormat="1">
+      <c r="A35" s="22"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" spans="1:7" customFormat="1">
+      <c r="A36" s="22"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="G36" s="22"/>
+    </row>
+    <row r="37" spans="1:7" customFormat="1">
+      <c r="A37" s="22"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="G37" s="22"/>
+    </row>
+    <row r="38" spans="1:7" customFormat="1">
+      <c r="A38" s="22"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="G38" s="22"/>
+    </row>
+    <row r="39" spans="1:7" customFormat="1">
+      <c r="A39" s="22"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="G39" s="22"/>
+    </row>
+    <row r="40" spans="1:7" customFormat="1">
+      <c r="A40" s="22"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="G40" s="22"/>
+    </row>
+    <row r="41" spans="1:7" customFormat="1">
+      <c r="A41" s="22"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="G41" s="22"/>
+    </row>
+    <row r="42" spans="1:7" customFormat="1">
+      <c r="A42" s="22"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="G42" s="22"/>
+    </row>
+    <row r="43" spans="1:7" customFormat="1">
+      <c r="A43" s="22"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="G43" s="22"/>
+    </row>
+    <row r="44" spans="1:7" customFormat="1">
+      <c r="A44" s="22"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="G44" s="22"/>
+    </row>
+    <row r="45" spans="1:7" customFormat="1">
+      <c r="A45" s="22"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="G45" s="22"/>
+    </row>
+    <row r="46" spans="1:7" customFormat="1">
+      <c r="A46" s="22"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="G46" s="22"/>
+    </row>
+    <row r="47" spans="1:7" customFormat="1">
+      <c r="A47" s="22"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="G47" s="22"/>
+    </row>
+    <row r="48" spans="1:7" customFormat="1">
+      <c r="A48" s="22"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="G48" s="22"/>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="22"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="G49" s="22"/>
+      <c r="I49"/>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="22"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="G50" s="22"/>
+      <c r="I50"/>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="22"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="G51" s="22"/>
+      <c r="I51"/>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="22"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="G52" s="22"/>
+      <c r="I52"/>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="22"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="G53" s="22"/>
+      <c r="I53"/>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="22"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="G54" s="22"/>
+      <c r="I54"/>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="22"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="G55" s="22"/>
+      <c r="I55"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -3488,13 +3549,13 @@
   <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="17" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.7109375" customWidth="1"/>
     <col min="9" max="9" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3531,233 +3592,501 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="7">
+        <v>45819</v>
+      </c>
+      <c r="C2" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="14">
+        <v>3450003315</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7">
+        <v>45819</v>
+      </c>
+      <c r="C3" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="14">
+        <v>3450003458</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
+      <c r="B4" s="7">
+        <v>45841</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D4" s="47">
+        <v>132825669</v>
+      </c>
+      <c r="E4" s="44">
+        <v>3449997991</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="23">
+        <v>45817</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
+      <c r="B5" s="7">
+        <v>45812</v>
+      </c>
+      <c r="C5" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D5" s="47">
+        <v>132831501</v>
+      </c>
+      <c r="E5" s="44">
+        <v>3449998596</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="23">
+        <v>45812</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
+      <c r="B6" s="7">
+        <v>45812</v>
+      </c>
+      <c r="C6" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D6" s="47">
+        <v>132836021</v>
+      </c>
+      <c r="E6" s="44">
+        <v>3449998915</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <v>45812</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="7">
+        <v>45812</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D7" s="47">
+        <v>132852923</v>
+      </c>
+      <c r="E7" s="44">
+        <v>3449999113</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="23">
+        <v>45812</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
+      <c r="B8" s="7">
+        <v>45813</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D8" s="47">
+        <v>132850480</v>
+      </c>
+      <c r="E8" s="44">
+        <v>3449999674</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="23">
+        <v>45813</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="7">
+        <v>45830</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D9" s="47">
+        <v>132890543</v>
+      </c>
+      <c r="E9" s="44">
+        <v>3450001709</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="23">
+        <v>45819</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="B10" s="7">
+        <v>45818</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D10" s="47">
+        <v>132910572</v>
+      </c>
+      <c r="E10" s="44">
+        <v>3450002600</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="23">
+        <v>45820</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="B11" s="7">
+        <v>45819</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D11" s="47">
+        <v>132917618</v>
+      </c>
+      <c r="E11" s="44">
+        <v>3450003029</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="23">
+        <v>45820</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="B12" s="7">
+        <v>45827</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D12" s="47">
+        <v>132908319</v>
+      </c>
+      <c r="E12" s="44">
+        <v>3450002457</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="23">
+        <v>45820</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="B13" s="7">
+        <v>45817</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D13" s="47">
+        <v>132909899</v>
+      </c>
+      <c r="E13" s="44">
+        <v>3450002237</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="23">
+        <v>45819</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="B14" s="7">
+        <v>45815</v>
+      </c>
+      <c r="C14" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D14" s="47">
+        <v>132882888</v>
+      </c>
+      <c r="E14" s="44">
+        <v>3450001490</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" s="23">
+        <v>45820</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
+      <c r="B15" s="7">
+        <v>45812</v>
+      </c>
+      <c r="C15" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D15" s="47">
+        <v>132826001</v>
+      </c>
+      <c r="E15" s="44">
+        <v>3449998190</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="23">
+        <v>45812</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
+      <c r="B16" s="7">
+        <v>45812</v>
+      </c>
+      <c r="C16" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D16" s="47">
+        <v>132827355</v>
+      </c>
+      <c r="E16" s="44">
+        <v>3449998300</v>
+      </c>
+      <c r="F16" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="23">
+        <v>45812</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
+      <c r="B17" s="7">
+        <v>45811</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D17" s="47">
+        <v>132833720</v>
+      </c>
+      <c r="E17" s="44">
+        <v>3449997837</v>
+      </c>
+      <c r="F17" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="23">
+        <v>45811</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
+      <c r="B18" s="7">
+        <v>45812</v>
+      </c>
+      <c r="C18" s="7">
+        <v>45820</v>
+      </c>
+      <c r="D18" s="47">
+        <v>132836068</v>
+      </c>
+      <c r="E18" s="44">
+        <v>3449998926</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <v>45812</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
+      <c r="D19" s="46"/>
       <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="20"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
+      <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4131,7 +4460,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6072,67 +6401,51 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-470937</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-470937</Url>
+      <Description>QAFFA7D2F2TC-2102087286-470937</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="32fbec5585ae01a22f32af5838af0c4d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b2552458edfdc024ce707f91c2c891f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6180,12 +6493,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -6194,12 +6507,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -6282,7 +6595,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6301,7 +6614,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6334,7 +6647,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6412,8 +6725,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6502,61 +6815,77 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-470937</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-470937</Url>
-      <Description>QAFFA7D2F2TC-2102087286-470937</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B9C84E2-EC62-4634-9EE9-B4EB3296D301}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75FBB85C-E500-466F-A910-4F2EB96A6878}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>